--- a/media/exports/reports/2026-10/growth.xlsx
+++ b/media/exports/reports/2026-10/growth.xlsx
@@ -30,50 +30,60 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="13"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
   </fonts>
@@ -105,35 +115,35 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1498,8 +1508,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3676,8 +3686,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6755,8 +6765,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6942,8 +6952,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10010,8 +10020,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10197,8 +10207,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-10/growth.xlsx
+++ b/media/exports/reports/2026-10/growth.xlsx
@@ -1047,7 +1047,7 @@
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>September's client work made $78,830 gross margin (59.8%). Consultant time not charged to client work took $1,980 and overheads $52,140, leaving $24,710 profit before tax (18.7% of revenue). To cover overheads, client work needs a 41.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>September's client work made $68,410 gross margin (51.9%). Consultant time not charged to client work took $660 and overheads $52,140, leaving $15,610 profit before tax (11.8% of revenue). To cover overheads, client work needs a 40.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>$259,430 before overheads</t>
+          <t>$248,170 before overheads</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
     <row r="79" ht="45" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Revenue is 47.8% up on the same period last year, year to date ($411,850 against $278,590). Retainers make the highest gross margin (69.9%); Projects the lowest (58.8%). The business needs 41.0% gross margin just to cover overheads.</t>
+          <t>Revenue is 47.8% up on the same period last year, year to date ($411,850 against $278,590). Retainers make the highest gross margin (68.5%); Projects the lowest (56.3%). The business needs 40.0% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Retainers: 69.9% gross margin, the most profitable work you do. Projects: 58.8% gross margin, the thinnest, still above the 41.0% overheads need.</t>
+          <t>Retainers: 68.5% gross margin, the most profitable work you do. Projects: 56.3% gross margin, the thinnest, still above the 40.0% overheads need.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>$148,950 before overheads</t>
+          <t>$142,550 before overheads</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Projects brought in $253,250 this financial year to date, 35.1% on the same period last year (slower than the business as a whole, 47.8%), at a 58.8% gross margin (below the 63.0% overall).</t>
+          <t>Projects brought in $253,250 this financial year to date, 35.1% on the same period last year (slower than the business as a whole, 47.8%), at a 56.3% gross margin (below the 60.3% overall).</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Projects: 58.8% gross margin, 17.8 points clear of the 41.0% overheads need.</t>
+          <t>Projects: 56.3% gross margin, 16.2 points clear of the 40.0% overheads need.</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>$90,820 before overheads</t>
+          <t>$89,020 before overheads</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
     <row r="103" ht="45" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Retainers brought in $130,000 this financial year to date, 99.4% on the same period last year (faster than the business as a whole, 47.8%), at a 69.9% gross margin (above the 63.0% overall).</t>
+          <t>Retainers brought in $130,000 this financial year to date, 99.4% on the same period last year (faster than the business as a whole, 47.8%), at a 68.5% gross margin (above the 60.3% overall).</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Retainers: 69.9% gross margin, 28.8 points clear of the 41.0% overheads need.</t>
+          <t>Retainers: 68.5% gross margin, 28.4 points clear of the 40.0% overheads need.</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>$19,660 before overheads</t>
+          <t>$16,600 before overheads</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Training brought in $28,600 this financial year to date, 10.4% on the same period last year (slower than the business as a whole, 47.8%), at a 68.7% gross margin (above the 63.0% overall).</t>
+          <t>Training brought in $28,600 this financial year to date, 10.4% on the same period last year (slower than the business as a whole, 47.8%), at a 58.0% gross margin (below the 60.3% overall).</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Training: 68.7% gross margin, 27.7 points clear of the 41.0% overheads need.</t>
+          <t>Training: 58.0% gross margin, 18.0 points clear of the 40.0% overheads need.</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="B149" s="12" t="n">
-        <v>78830</v>
+        <v>68410</v>
       </c>
     </row>
     <row r="150">
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="B151" s="12" t="n">
-        <v>44520</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="152">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="B178" s="12" t="n">
-        <v>259430</v>
+        <v>248170</v>
       </c>
     </row>
     <row r="179">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="B189" s="12" t="n">
-        <v>259430</v>
+        <v>248170</v>
       </c>
     </row>
     <row r="190">
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="B209" s="12" t="n">
-        <v>148950</v>
+        <v>142550</v>
       </c>
     </row>
     <row r="210">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="B220" s="12" t="n">
-        <v>148950</v>
+        <v>142550</v>
       </c>
     </row>
     <row r="221">
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="B240" s="12" t="n">
-        <v>90820</v>
+        <v>89020</v>
       </c>
     </row>
     <row r="241">
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="B251" s="12" t="n">
-        <v>90820</v>
+        <v>89020</v>
       </c>
     </row>
     <row r="252">
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="B271" s="12" t="n">
-        <v>19660</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="272">
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="B282" s="12" t="n">
-        <v>19660</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="283">
@@ -7710,7 +7710,7 @@
         <v>114640</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>45780</v>
+        <v>46620</v>
       </c>
       <c r="F27" s="12">
         <f>D27-E27</f>
@@ -7741,7 +7741,7 @@
         <v>131850</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>53020</v>
+        <v>63440</v>
       </c>
       <c r="F28" s="12">
         <f>D28-E28</f>
@@ -8485,7 +8485,7 @@
         <v>85950</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>36400</v>
+        <v>42800</v>
       </c>
       <c r="F52" s="12">
         <f>D52-E52</f>
@@ -9198,7 +9198,7 @@
         <v>32500</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>12000</v>
+        <v>12840</v>
       </c>
       <c r="F75" s="12">
         <f>D75-E75</f>
@@ -9229,7 +9229,7 @@
         <v>32500</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>12480</v>
+        <v>13440</v>
       </c>
       <c r="F76" s="12">
         <f>D76-E76</f>
@@ -9973,7 +9973,7 @@
         <v>13400</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>4140</v>
+        <v>7200</v>
       </c>
       <c r="F100" s="12">
         <f>D100-E100</f>
@@ -10123,7 +10123,7 @@
         <v/>
       </c>
       <c r="E6" s="12" t="n">
-        <v>148950</v>
+        <v>142550</v>
       </c>
       <c r="F6" s="13">
         <f>IF(B6=0,"",E6/B6)</f>
@@ -10147,7 +10147,7 @@
         <v/>
       </c>
       <c r="E7" s="12" t="n">
-        <v>90820</v>
+        <v>89020</v>
       </c>
       <c r="F7" s="13">
         <f>IF(B7=0,"",E7/B7)</f>
@@ -10171,7 +10171,7 @@
         <v/>
       </c>
       <c r="E8" s="12" t="n">
-        <v>19660</v>
+        <v>16600</v>
       </c>
       <c r="F8" s="13">
         <f>IF(B8=0,"",E8/B8)</f>
@@ -10195,7 +10195,7 @@
         <v/>
       </c>
       <c r="E9" s="12" t="n">
-        <v>259430</v>
+        <v>248170</v>
       </c>
       <c r="F9" s="13">
         <f>IF(B9=0,"",E9/B9)</f>

--- a/media/exports/reports/2026-10/growth.xlsx
+++ b/media/exports/reports/2026-10/growth.xlsx
@@ -576,14 +576,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+          <t>From gross margin to profit · latest closed month: September</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>September's jobs made $73,107 gross margin (36.1%). Technician time not charged to jobs took $3,430 and overheads $59,580, leaving $10,097 profit before tax (5.0% of revenue). To cover overheads, jobs need a 31.1% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's jobs made $73,107 gross margin (36.1%). Technician time not charged to jobs took $3,430 and overheads $59,580, leaving $10,097 profit before tax (5.0% of revenue). To cover overheads, jobs need a 31.1% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -683,10 +683,10 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts: 59.5% gross margin, the most profitable work you do. Installations: 28.8% gross margin, below the 31.1% needed to cover overheads.</t>
+          <t>Installations: 28.8% gross margin, 6.2 points under the 35.0% target: about $24,765 on $400,900 of revenue this financial year to date. It's below the 31.1% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($39,764 ahead on $162,000 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts: 59.5% gross margin, 28.4 points clear of the 31.1% overheads need.</t>
+          <t>Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($39,764 ahead on $162,000 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Installations: 28.8% gross margin, below the 31.1% needed to cover overheads.</t>
+          <t>Installations: 28.8% gross margin, 6.2 points under the 35.0% target: about $24,765 on $400,900 of revenue this financial year to date. It's below the 31.1% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: 43.7% gross margin, 12.6 points clear of the 31.1% overheads need.</t>
+          <t>Call-outs and repairs: 43.7% gross margin, 8.7 points over the 35.0% target ($7,747 ahead on $88,564 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1040,14 +1040,14 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="60" customHeight="1">
+          <t>From gross margin to profit · latest closed month: September</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="75" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>September's client work made $68,410 gross margin (51.9%). Consultant time not charged to client work took $660 and overheads $52,140, leaving $15,610 profit before tax (11.8% of revenue). To cover overheads, client work needs a 40.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's client work made $68,410 gross margin (51.9%). Consultant time not charged to client work took $660 and overheads $52,140, leaving $15,610 profit before tax (11.8% of revenue). To cover overheads, client work needs a 40.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="30" customHeight="1">
+    <row r="82" ht="45" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Retainers: 68.5% gross margin, the most profitable work you do. Projects: 56.3% gross margin, the thinnest, still above the 40.0% overheads need.</t>
+          <t>Projects: 56.3% gross margin, 16.3 points over the 40.0% target ($41,250 ahead on $253,250 this financial year to date). Retainers: 68.5% gross margin, 28.5 points over the 40.0% target ($37,020 ahead on $130,000 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Projects: 56.3% gross margin, 16.2 points clear of the 40.0% overheads need.</t>
+          <t>Projects: 56.3% gross margin, 16.3 points over the 40.0% target ($41,250 ahead on $253,250 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Retainers: 68.5% gross margin, 28.4 points clear of the 40.0% overheads need.</t>
+          <t>Retainers: 68.5% gross margin, 28.5 points over the 40.0% target ($37,020 ahead on $130,000 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Training: 58.0% gross margin, 18.0 points clear of the 40.0% overheads need.</t>
+          <t>Training: 58.0% gross margin, 18.0 points over the 40.0% target ($5,160 ahead on $28,600 this financial year to date).</t>
         </is>
       </c>
     </row>

--- a/media/exports/reports/2026-10/growth.xlsx
+++ b/media/exports/reports/2026-10/growth.xlsx
@@ -15,10 +15,40 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year to date Services" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="Trades_October_so_far_against_October_last_year">'Report'!$B$16</definedName>
+    <definedName name="Trades_Year_to_date_against_the_same_period_last_year">'Report'!$B$17</definedName>
+    <definedName name="Trades_Gross_margin_year_to_date">'Report'!$B$18</definedName>
+    <definedName name="Trades_October_so_far_against_October_last_year_2">'Report'!$B$28</definedName>
+    <definedName name="Trades_Year_to_date_against_the_same_period_last_year_2">'Report'!$B$29</definedName>
+    <definedName name="Trades_Gross_margin_year_to_date_2">'Report'!$B$30</definedName>
+    <definedName name="Trades_October_so_far_against_October_last_year_3">'Report'!$B$40</definedName>
+    <definedName name="Trades_Year_to_date_against_the_same_period_last_year_3">'Report'!$B$41</definedName>
+    <definedName name="Trades_Gross_margin_year_to_date_3">'Report'!$B$42</definedName>
+    <definedName name="Trades_October_so_far_against_October_last_year_4">'Report'!$B$52</definedName>
+    <definedName name="Trades_Year_to_date_against_the_same_period_last_year_4">'Report'!$B$53</definedName>
+    <definedName name="Trades_Gross_margin_year_to_date_4">'Report'!$B$54</definedName>
+    <definedName name="Services_October_so_far_against_October_last_year">'Report'!$B$74</definedName>
+    <definedName name="Services_Year_to_date_against_the_same_period_last_year">'Report'!$B$75</definedName>
+    <definedName name="Services_Gross_margin_year_to_date">'Report'!$B$76</definedName>
+    <definedName name="Services_October_so_far_against_October_last_year_2">'Report'!$B$86</definedName>
+    <definedName name="Services_Year_to_date_against_the_same_period_last_year_2">'Report'!$B$87</definedName>
+    <definedName name="Services_Gross_margin_year_to_date_2">'Report'!$B$88</definedName>
+    <definedName name="Services_October_so_far_against_October_last_year_3">'Report'!$B$98</definedName>
+    <definedName name="Services_Year_to_date_against_the_same_period_last_year_3">'Report'!$B$99</definedName>
+    <definedName name="Services_Gross_margin_year_to_date_3">'Report'!$B$100</definedName>
+    <definedName name="Services_October_so_far_against_October_last_year_4">'Report'!$B$110</definedName>
+    <definedName name="Services_Year_to_date_against_the_same_period_last_year_4">'Report'!$B$111</definedName>
+    <definedName name="Services_Gross_margin_year_to_date_4">'Report'!$B$112</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$121</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$284</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data Trades'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data Trades'!$A$1:$G$101</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year to date Trades'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Year to date Trades'!$A$1:$F$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Data Services'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Data Services'!$A$1:$G$101</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Year to date Services'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Year to date Services'!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,11 +91,6 @@
       <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
@@ -81,6 +106,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="002F7A5D"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -125,25 +155,27 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -221,6 +253,538 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Revenue by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>All</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Trades'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Trades'!$D$6:$D$29</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Maintenance contracts</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Trades'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Trades'!$D$30:$D$53</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Installations</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Trades'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Trades'!$D$54:$D$77</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Call-outs and repairs</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5F6F63"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Trades'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Trades'!$D$78:$D$101</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Revenue by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>All</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Services'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Services'!$D$6:$D$29</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Projects</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Services'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Services'!$D$30:$D$53</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Retainers</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Services'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Services'!$D$54:$D$77</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Training</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5F6F63"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Services'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Services'!$D$78:$D$101</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="growth_Data_Trades" displayName="growth_Data_Trades" ref="A5:G101" headerRowCount="1">
+  <autoFilter ref="A5:G101"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Direct cost"/>
+    <tableColumn id="6" name="Gross margin"/>
+    <tableColumn id="7" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="growth_Year_to_date_Trades" displayName="growth_Year_to_date_Trades" ref="A5:F9" headerRowCount="1">
+  <autoFilter ref="A5:F9"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Year to date"/>
+    <tableColumn id="3" name="Same period last year"/>
+    <tableColumn id="4" name="Growth"/>
+    <tableColumn id="5" name="Gross margin $"/>
+    <tableColumn id="6" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="growth_Data_Services" displayName="growth_Data_Services" ref="A5:G101" headerRowCount="1">
+  <autoFilter ref="A5:G101"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Direct cost"/>
+    <tableColumn id="6" name="Gross margin"/>
+    <tableColumn id="7" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="growth_Year_to_date_Services" displayName="growth_Year_to_date_Services" ref="A5:F9" headerRowCount="1">
+  <autoFilter ref="A5:F9"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Year to date"/>
+    <tableColumn id="3" name="Same period last year"/>
+    <tableColumn id="4" name="Growth"/>
+    <tableColumn id="5" name="Gross margin $"/>
+    <tableColumn id="6" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -531,7 +1095,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -561,14 +1125,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Gross margin, not profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>From gross margin to profit · latest closed month: September</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's jobs made $73,107 gross margin (36.1%). Technician time not charged to jobs took $3,430 and overheads $59,580, leaving $10,097 profit before tax (5.0% of revenue). To cover overheads, jobs need a 31.1% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -576,14 +1140,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit · latest closed month: September</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="75" customHeight="1">
+          <t>Gross margin, not profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's jobs made $73,107 gross margin (36.1%). Technician time not charged to jobs took $3,430 and overheads $59,580, leaving $10,097 profit before tax (5.0% of revenue). To cover overheads, jobs need a 31.1% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1589,14 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Gross margin, not profit</t>
+          <t>From gross margin to profit · latest closed month: September</t>
         </is>
       </c>
     </row>
     <row r="67" ht="75" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's client work made $68,410 gross margin (51.9%). Consultant time not charged to client work took $660 and overheads $52,140, leaving $15,610 profit before tax (11.8% of revenue). To cover overheads, client work needs a 40.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -1040,14 +1604,14 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit · latest closed month: September</t>
+          <t>Gross margin, not profit</t>
         </is>
       </c>
     </row>
     <row r="70" ht="75" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's client work made $68,410 gross margin (51.9%). Consultant time not charged to client work took $660 and overheads $52,140, leaving $15,610 profit before tax (11.8% of revenue). To cover overheads, client work needs a 40.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
         </is>
       </c>
     </row>
@@ -1550,7 +2114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -3735,7 +4299,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -6777,6 +7341,10 @@
     <brk id="53" min="0" max="16383" man="1"/>
     <brk id="77" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -6807,7 +7375,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -6959,6 +7527,9 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -6990,7 +7561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -10032,6 +10603,10 @@
     <brk id="53" min="0" max="16383" man="1"/>
     <brk id="77" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -10062,7 +10637,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -10214,5 +10789,8 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>